--- a/Misc/Data/mBasicInt1.xlsx
+++ b/Misc/Data/mBasicInt1.xlsx
@@ -545,17 +545,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -571,7 +571,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -579,7 +579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -587,7 +587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -595,7 +595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -603,7 +603,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -611,7 +611,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -619,7 +619,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -627,7 +627,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -635,7 +635,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -643,7 +643,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -660,17 +660,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="25.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -693,7 +693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -733,7 +733,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -758,16 +758,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.15234375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -784,7 +784,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -801,7 +801,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>59</v>
       </c>
@@ -812,7 +812,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>59</v>
       </c>
@@ -823,7 +823,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>59</v>
       </c>
@@ -843,12 +843,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>48</v>
       </c>
@@ -856,7 +856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -864,7 +864,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -880,12 +880,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -902,7 +902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -961,15 +961,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>26</v>
       </c>
@@ -989,7 +989,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>8.6111111111111107</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>8.1388888888888893</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1082,13 +1082,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1166,12 +1166,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
